--- a/data/trans_orig/P24B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51677</t>
+          <t>51645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79040</t>
+          <t>81748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80117</t>
+          <t>79386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114472</t>
+          <t>115129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247754</t>
+          <t>246955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280629</t>
+          <t>280940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95016</t>
+          <t>96062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121984</t>
+          <t>121351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352798</t>
+          <t>351736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393218</t>
+          <t>393904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58132</t>
+          <t>57604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47029</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65882</t>
+          <t>63639</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98749</t>
+          <t>97213</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96801</t>
+          <t>95717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139334</t>
+          <t>137701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77204</t>
+          <t>73614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114182</t>
+          <t>112710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182787</t>
+          <t>183260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235516</t>
+          <t>237045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>551841</t>
+          <t>553420</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>606887</t>
+          <t>607898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>308184</t>
+          <t>308031</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>353780</t>
+          <t>353107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>876407</t>
+          <t>875234</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>948195</t>
+          <t>944386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99532</t>
+          <t>102941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141711</t>
+          <t>141705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105306</t>
+          <t>105887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143950</t>
+          <t>142887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215429</t>
+          <t>218592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270758</t>
+          <t>273272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>46063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>45899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54977</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85609</t>
+          <t>84707</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116155</t>
+          <t>115704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144100</t>
+          <t>142825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75862</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98431</t>
+          <t>97395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196115</t>
+          <t>200278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233709</t>
+          <t>235372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39171</t>
+          <t>39496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26812</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60733</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>190066</t>
+          <t>189440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>243889</t>
+          <t>242929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>138394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185240</t>
+          <t>184899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>340076</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>413113</t>
+          <t>412919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>940124</t>
+          <t>939685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1007518</t>
+          <t>1008922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>500371</t>
+          <t>499663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>557430</t>
+          <t>555900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1456691</t>
+          <t>1455238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1544929</t>
+          <t>1549496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167205</t>
+          <t>164819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217492</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>152551</t>
+          <t>155027</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200007</t>
+          <t>200549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>335468</t>
+          <t>335610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>404987</t>
+          <t>405865</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>83979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119843</t>
+          <t>119317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67288</t>
+          <t>66585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134864</t>
+          <t>135550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176299</t>
+          <t>178469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>156723</t>
+          <t>156891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193500</t>
+          <t>194704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91269</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120833</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257502</t>
+          <t>257707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>304431</t>
+          <t>304718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44169</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73678</t>
+          <t>72583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>30664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54024</t>
+          <t>53458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81110</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119688</t>
+          <t>119349</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>232690</t>
+          <t>234270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290685</t>
+          <t>291557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131676</t>
+          <t>130218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177344</t>
+          <t>177117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379652</t>
+          <t>378106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450938</t>
+          <t>450311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>432511</t>
+          <t>430830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>493808</t>
+          <t>492064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>310399</t>
+          <t>308686</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>361339</t>
+          <t>364062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>758217</t>
+          <t>758641</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>839674</t>
+          <t>839423</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110040</t>
+          <t>108398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152813</t>
+          <t>151564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125546</t>
+          <t>125344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170433</t>
+          <t>170018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243994</t>
+          <t>245705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308438</t>
+          <t>304667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>54703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39610</t>
+          <t>39277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63500</t>
+          <t>63150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76677</t>
+          <t>77285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110185</t>
+          <t>110830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76218</t>
+          <t>77186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>103389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57444</t>
+          <t>56545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83079</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143174</t>
+          <t>142111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179119</t>
+          <t>179880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>18962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>41052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35228</t>
+          <t>34676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64416</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>368379</t>
+          <t>369380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>439674</t>
+          <t>440450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229081</t>
+          <t>229976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286122</t>
+          <t>286682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>621544</t>
+          <t>622278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>712256</t>
+          <t>711679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>691860</t>
+          <t>688453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>764327</t>
+          <t>766959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480057</t>
+          <t>477272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>546715</t>
+          <t>543528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1188556</t>
+          <t>1190994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1291756</t>
+          <t>1289073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190238</t>
+          <t>190917</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>246862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>181764</t>
+          <t>182084</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>234812</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384074</t>
+          <t>383228</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>463924</t>
+          <t>462844</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016 (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51027</t>
+          <t>50739</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80033</t>
+          <t>79345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150256</t>
+          <t>150084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175975</t>
+          <t>176972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80380</t>
+          <t>80265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100928</t>
+          <t>102324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239579</t>
+          <t>237029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273110</t>
+          <t>271600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27452</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159128</t>
+          <t>157578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209707</t>
+          <t>207369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120540</t>
+          <t>122070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164436</t>
+          <t>164426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295339</t>
+          <t>293410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358363</t>
+          <t>359915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>482214</t>
+          <t>484527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>539713</t>
+          <t>539023</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>404048</t>
+          <t>405167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>454298</t>
+          <t>453475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>897037</t>
+          <t>900202</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>974797</t>
+          <t>976584</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86669</t>
+          <t>85596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126292</t>
+          <t>127966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71850</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106441</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166837</t>
+          <t>170040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218515</t>
+          <t>224687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46948</t>
+          <t>48271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76216</t>
+          <t>77066</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77968</t>
+          <t>79546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101204</t>
+          <t>102611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59990</t>
+          <t>59623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81728</t>
+          <t>81177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146387</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178353</t>
+          <t>176761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25425</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41865</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223910</t>
+          <t>223304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>279195</t>
+          <t>281237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172482</t>
+          <t>173898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>226122</t>
+          <t>224339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>414534</t>
+          <t>415572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>489125</t>
+          <t>487657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>735398</t>
+          <t>732540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>802969</t>
+          <t>802382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>560004</t>
+          <t>564319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>620170</t>
+          <t>622646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1313946</t>
+          <t>1316410</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403384</t>
+          <t>1401455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115717</t>
+          <t>118464</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>165213</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103695</t>
+          <t>104463</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>144575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231810</t>
+          <t>232491</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>294176</t>
+          <t>295453</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51645</t>
+          <t>51671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81748</t>
+          <t>79184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>44735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79386</t>
+          <t>81809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115129</t>
+          <t>117529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246955</t>
+          <t>246558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280940</t>
+          <t>280995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96062</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121351</t>
+          <t>120713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>351736</t>
+          <t>349835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393904</t>
+          <t>393136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57604</t>
+          <t>58426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>45579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>62569</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97213</t>
+          <t>96684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95717</t>
+          <t>99660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137701</t>
+          <t>139615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>75241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112710</t>
+          <t>111050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183260</t>
+          <t>178105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237045</t>
+          <t>235537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>553420</t>
+          <t>550301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>607898</t>
+          <t>602787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>308031</t>
+          <t>308620</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>353107</t>
+          <t>354365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>875234</t>
+          <t>877021</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>944386</t>
+          <t>947189</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102941</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141705</t>
+          <t>143590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105887</t>
+          <t>105074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142887</t>
+          <t>143987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218592</t>
+          <t>217053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273272</t>
+          <t>275711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>46698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45899</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84707</t>
+          <t>85521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115704</t>
+          <t>116181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142825</t>
+          <t>142826</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>73491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97395</t>
+          <t>96520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200278</t>
+          <t>198204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235372</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,47%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>39701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>28033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>60604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189440</t>
+          <t>188031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242929</t>
+          <t>242758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138394</t>
+          <t>138517</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184899</t>
+          <t>184218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340076</t>
+          <t>344624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412919</t>
+          <t>416003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>939685</t>
+          <t>940290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1008922</t>
+          <t>1011181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>499663</t>
+          <t>498398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>555900</t>
+          <t>553817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1455238</t>
+          <t>1457953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1549496</t>
+          <t>1542820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164819</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>220542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155027</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200549</t>
+          <t>200373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>335610</t>
+          <t>334350</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>405865</t>
+          <t>404758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83979</t>
+          <t>85714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119317</t>
+          <t>119082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66585</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135550</t>
+          <t>133663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178469</t>
+          <t>176724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>156891</t>
+          <t>157105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194704</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90585</t>
+          <t>89699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119569</t>
+          <t>119902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257707</t>
+          <t>257353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>304718</t>
+          <t>305489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44142</t>
+          <t>44775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72583</t>
+          <t>73575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30664</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53458</t>
+          <t>54155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82493</t>
+          <t>80610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>118586</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234270</t>
+          <t>235438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291557</t>
+          <t>291926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177117</t>
+          <t>177016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>378106</t>
+          <t>379177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450311</t>
+          <t>452799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>430830</t>
+          <t>431766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>492064</t>
+          <t>490324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>308686</t>
+          <t>311036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>364062</t>
+          <t>362456</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>758641</t>
+          <t>754508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>839423</t>
+          <t>836257</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108398</t>
+          <t>109907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151564</t>
+          <t>152243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125344</t>
+          <t>125051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170018</t>
+          <t>168753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245705</t>
+          <t>247324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304667</t>
+          <t>307478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>29115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54703</t>
+          <t>54433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39277</t>
+          <t>39382</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63150</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77285</t>
+          <t>76862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110830</t>
+          <t>110971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77186</t>
+          <t>77465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103389</t>
+          <t>105170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56545</t>
+          <t>57868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81942</t>
+          <t>82818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142111</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>178625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41052</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64118</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>369380</t>
+          <t>370921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440450</t>
+          <t>440564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229976</t>
+          <t>229875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286682</t>
+          <t>286355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>618408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>711679</t>
+          <t>711986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>688453</t>
+          <t>686461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>766959</t>
+          <t>763828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477272</t>
+          <t>479688</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>543528</t>
+          <t>545286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1190994</t>
+          <t>1192612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1289073</t>
+          <t>1290301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190917</t>
+          <t>187790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>246862</t>
+          <t>246604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182084</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234812</t>
+          <t>232260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>383228</t>
+          <t>384925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>462844</t>
+          <t>462554</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28252</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>50913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79345</t>
+          <t>80163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150084</t>
+          <t>149665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176972</t>
+          <t>176872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80265</t>
+          <t>78547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102324</t>
+          <t>102371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237029</t>
+          <t>239037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>271600</t>
+          <t>272917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,04%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>28241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>53124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157578</t>
+          <t>159625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207369</t>
+          <t>206640</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122070</t>
+          <t>122968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164426</t>
+          <t>164782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>293410</t>
+          <t>289096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359915</t>
+          <t>357219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>484527</t>
+          <t>485298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>539023</t>
+          <t>539583</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>405167</t>
+          <t>401190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>453475</t>
+          <t>453037</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>900202</t>
+          <t>905932</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976584</t>
+          <t>979162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85596</t>
+          <t>88317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127966</t>
+          <t>129295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70982</t>
+          <t>71562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>109465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>170040</t>
+          <t>169229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224687</t>
+          <t>222661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>40649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48271</t>
+          <t>48581</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77066</t>
+          <t>77708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79546</t>
+          <t>79390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102611</t>
+          <t>101320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59623</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145896</t>
+          <t>146006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176761</t>
+          <t>178221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25523</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19762</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223304</t>
+          <t>225589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>281237</t>
+          <t>285074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173898</t>
+          <t>173557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224339</t>
+          <t>225363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>415572</t>
+          <t>413034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>487657</t>
+          <t>491563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>732540</t>
+          <t>733001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>802382</t>
+          <t>800415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>564319</t>
+          <t>563639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622646</t>
+          <t>618166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1316410</t>
+          <t>1315010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401455</t>
+          <t>1399700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118464</t>
+          <t>118412</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165213</t>
+          <t>163379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104463</t>
+          <t>103697</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>144575</t>
+          <t>144797</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>232491</t>
+          <t>232720</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295453</t>
+          <t>296919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
